--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.12859104598006</v>
+        <v>73.95876212200862</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.31839562056474</v>
+        <v>77.4926531368628</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69.35238037194912</v>
+        <v>65.71301642068219</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.152742662118417</v>
+        <v>2.149529609555394</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.669300382063744e-24</v>
+        <v>1.663538331216459e-24</v>
       </c>
     </row>
     <row r="16">
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>822.3186666666668</v>
+        <v>723.0912279822078</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>882.176</v>
+        <v>794.8584138329527</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88.54000000000001</v>
+        <v>73.25882950156915</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>2886.470666666667</v>
+        <v>2684.644471316729</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>83.31839562056474</v>
+        <v>77.4926531368628</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84.83570161267836</v>
+        <v>78.84287412960116</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.51730599211362</v>
+        <v>-1.350220992738357</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>74.56939890085761</v>
+        <v>69.96680994254842</v>
       </c>
       <c r="F11" t="n">
-        <v>58.96359303115382</v>
+        <v>55.32422907988689</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>69.35238037194912</v>
+        <v>65.71301642068219</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69.03497477089491</v>
+        <v>64.89911163171776</v>
       </c>
       <c r="C2" t="n">
-        <v>73.67811039657761</v>
+        <v>69.02526436500332</v>
       </c>
       <c r="D2" t="n">
-        <v>78.32124602226033</v>
+        <v>73.15141709828889</v>
       </c>
       <c r="E2" t="n">
-        <v>82.96438164794304</v>
+        <v>77.27756983157447</v>
       </c>
       <c r="F2" t="n">
-        <v>87.60751727362575</v>
+        <v>81.40372256486002</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.43864728275476</v>
+        <v>65.30278414357761</v>
       </c>
       <c r="C3" t="n">
-        <v>74.08178290843748</v>
+        <v>69.42893687686318</v>
       </c>
       <c r="D3" t="n">
-        <v>78.72491853412019</v>
+        <v>73.55508961014876</v>
       </c>
       <c r="E3" t="n">
-        <v>83.36805415980291</v>
+        <v>77.68124234343432</v>
       </c>
       <c r="F3" t="n">
-        <v>88.01118978548561</v>
+        <v>81.80739507671989</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.84231979461462</v>
+        <v>65.70645665543748</v>
       </c>
       <c r="C4" t="n">
-        <v>74.48545542029734</v>
+        <v>69.83260938872304</v>
       </c>
       <c r="D4" t="n">
-        <v>79.12859104598006</v>
+        <v>73.95876212200862</v>
       </c>
       <c r="E4" t="n">
-        <v>83.77172667166276</v>
+        <v>78.08491485529419</v>
       </c>
       <c r="F4" t="n">
-        <v>88.41486229734548</v>
+        <v>82.21106758857975</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.24599230647449</v>
+        <v>66.11012916729734</v>
       </c>
       <c r="C5" t="n">
-        <v>74.88912793215721</v>
+        <v>70.23628190058291</v>
       </c>
       <c r="D5" t="n">
-        <v>79.53226355783993</v>
+        <v>74.36243463386849</v>
       </c>
       <c r="E5" t="n">
-        <v>84.17539918352263</v>
+        <v>78.48858736715405</v>
       </c>
       <c r="F5" t="n">
-        <v>88.81853480920535</v>
+        <v>82.61474010043962</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70.64966481833436</v>
+        <v>66.51380167915721</v>
       </c>
       <c r="C6" t="n">
-        <v>75.29280044401708</v>
+        <v>70.63995441244278</v>
       </c>
       <c r="D6" t="n">
-        <v>79.93593606969978</v>
+        <v>74.76610714572834</v>
       </c>
       <c r="E6" t="n">
-        <v>84.5790716953825</v>
+        <v>78.89225987901392</v>
       </c>
       <c r="F6" t="n">
-        <v>89.2222073210652</v>
+        <v>83.01841261229949</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>84.81</v>
+        <v>79.64</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>86.36</v>
+        <v>81.19</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>86.88</v>
+        <v>81.70999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.95876212200862</v>
+        <v>73.92437318755675</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77.4926531368628</v>
+        <v>77.45388065784299</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65.71301642068219</v>
+        <v>65.6888557568889</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.149529609555394</v>
+        <v>2.149480677904693</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.663538331216459e-24</v>
+        <v>1.663527524415819e-24</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>723.0912279822078</v>
+        <v>721.7479997247373</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>2684.644471316729</v>
+        <v>2683.301243059259</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.4926531368628</v>
+        <v>77.45388065784299</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78.84287412960116</v>
+        <v>78.80315977639378</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.350220992738357</v>
+        <v>-1.349279118550797</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>69.96680994254842</v>
+        <v>69.9362547120495</v>
       </c>
       <c r="F11" t="n">
-        <v>55.32422907988689</v>
+        <v>55.3000684160936</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>65.71301642068219</v>
+        <v>65.6888557568889</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.89911163171776</v>
+        <v>64.87160048415628</v>
       </c>
       <c r="C2" t="n">
-        <v>69.02526436500332</v>
+        <v>68.99431432399665</v>
       </c>
       <c r="D2" t="n">
-        <v>73.15141709828889</v>
+        <v>73.11702816383703</v>
       </c>
       <c r="E2" t="n">
-        <v>77.27756983157447</v>
+        <v>77.23974200367742</v>
       </c>
       <c r="F2" t="n">
-        <v>81.40372256486002</v>
+        <v>81.36245584351781</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.30278414357761</v>
+        <v>65.27527299601614</v>
       </c>
       <c r="C3" t="n">
-        <v>69.42893687686318</v>
+        <v>69.39798683585651</v>
       </c>
       <c r="D3" t="n">
-        <v>73.55508961014876</v>
+        <v>73.5207006756969</v>
       </c>
       <c r="E3" t="n">
-        <v>77.68124234343432</v>
+        <v>77.64341451553727</v>
       </c>
       <c r="F3" t="n">
-        <v>81.80739507671989</v>
+        <v>81.76612835537767</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.70645665543748</v>
+        <v>65.67894550787599</v>
       </c>
       <c r="C4" t="n">
-        <v>69.83260938872304</v>
+        <v>69.80165934771638</v>
       </c>
       <c r="D4" t="n">
-        <v>73.95876212200862</v>
+        <v>73.92437318755675</v>
       </c>
       <c r="E4" t="n">
-        <v>78.08491485529419</v>
+        <v>78.04708702739714</v>
       </c>
       <c r="F4" t="n">
-        <v>82.21106758857975</v>
+        <v>82.16980086723754</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.11012916729734</v>
+        <v>66.08261801973586</v>
       </c>
       <c r="C5" t="n">
-        <v>70.23628190058291</v>
+        <v>70.20533185957625</v>
       </c>
       <c r="D5" t="n">
-        <v>74.36243463386849</v>
+        <v>74.32804569941662</v>
       </c>
       <c r="E5" t="n">
-        <v>78.48858736715405</v>
+        <v>78.45075953925701</v>
       </c>
       <c r="F5" t="n">
-        <v>82.61474010043962</v>
+        <v>82.57347337909739</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.51380167915721</v>
+        <v>66.48629053159573</v>
       </c>
       <c r="C6" t="n">
-        <v>70.63995441244278</v>
+        <v>70.6090043714361</v>
       </c>
       <c r="D6" t="n">
-        <v>74.76610714572834</v>
+        <v>74.73171821127649</v>
       </c>
       <c r="E6" t="n">
-        <v>78.89225987901392</v>
+        <v>78.85443205111687</v>
       </c>
       <c r="F6" t="n">
-        <v>83.01841261229949</v>
+        <v>82.97714589095726</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>79.64</v>
+        <v>79.61</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>81.19</v>
+        <v>81.15000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>81.70999999999999</v>
+        <v>81.67</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.8</v>
+        <v>72.76000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.663527524415819e-24</v>
+        <v>47854.98768521653</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>0.5673324960156174</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.76000000000001</v>
+        <v>74.06999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47854.98768521653</v>
+        <v>88915.36410057644</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5673324960156174</v>
+        <v>1.054113226005508</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.06999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88915.36410057644</v>
+        <v>39705.5999997249</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.054113226005508</v>
+        <v>0.4707195267046425</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.92437318755675</v>
+        <v>73.94264839440076</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77.45388065784299</v>
+        <v>77.47448376411621</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65.6888557568889</v>
+        <v>65.70169919839807</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.149480677904693</v>
+        <v>2.149430670548544</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39705.5999997249</v>
+        <v>39131.30728097478</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4707195267046425</v>
+        <v>0.4639286728662899</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>794.8584138329527</v>
+        <v>795.5721849210412</v>
       </c>
     </row>
     <row r="4">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>2683.301243059259</v>
+        <v>2684.015014147347</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.45388065784299</v>
+        <v>77.47448376411621</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78.80315977639378</v>
+        <v>78.82437016971797</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.349279118550797</v>
+        <v>-1.349886405601751</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>69.9362547120495</v>
+        <v>69.95249740798987</v>
       </c>
       <c r="F11" t="n">
-        <v>55.3000684160936</v>
+        <v>55.31291185760276</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>65.6888557568889</v>
+        <v>65.70169919839807</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.87160048415628</v>
+        <v>64.88622064963147</v>
       </c>
       <c r="C2" t="n">
-        <v>68.99431432399665</v>
+        <v>69.01076201015624</v>
       </c>
       <c r="D2" t="n">
-        <v>73.11702816383703</v>
+        <v>73.13530337068104</v>
       </c>
       <c r="E2" t="n">
-        <v>77.23974200367742</v>
+        <v>77.25984473120582</v>
       </c>
       <c r="F2" t="n">
-        <v>81.36245584351781</v>
+        <v>81.3843860917306</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.27527299601614</v>
+        <v>65.28989316149134</v>
       </c>
       <c r="C3" t="n">
-        <v>69.39798683585651</v>
+        <v>69.41443452201611</v>
       </c>
       <c r="D3" t="n">
-        <v>73.5207006756969</v>
+        <v>73.5389758825409</v>
       </c>
       <c r="E3" t="n">
-        <v>77.64341451553727</v>
+        <v>77.66351724306568</v>
       </c>
       <c r="F3" t="n">
-        <v>81.76612835537767</v>
+        <v>81.78805860359047</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.67894550787599</v>
+        <v>65.6935656733512</v>
       </c>
       <c r="C4" t="n">
-        <v>69.80165934771638</v>
+        <v>69.81810703387598</v>
       </c>
       <c r="D4" t="n">
-        <v>73.92437318755675</v>
+        <v>73.94264839440076</v>
       </c>
       <c r="E4" t="n">
-        <v>78.04708702739714</v>
+        <v>78.06718975492555</v>
       </c>
       <c r="F4" t="n">
-        <v>82.16980086723754</v>
+        <v>82.19173111545034</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.08261801973586</v>
+        <v>66.09723818521107</v>
       </c>
       <c r="C5" t="n">
-        <v>70.20533185957625</v>
+        <v>70.22177954573584</v>
       </c>
       <c r="D5" t="n">
-        <v>74.32804569941662</v>
+        <v>74.34632090626063</v>
       </c>
       <c r="E5" t="n">
-        <v>78.45075953925701</v>
+        <v>78.47086226678542</v>
       </c>
       <c r="F5" t="n">
-        <v>82.57347337909739</v>
+        <v>82.59540362731019</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.48629053159573</v>
+        <v>66.50091069707094</v>
       </c>
       <c r="C6" t="n">
-        <v>70.6090043714361</v>
+        <v>70.62545205759571</v>
       </c>
       <c r="D6" t="n">
-        <v>74.73171821127649</v>
+        <v>74.7499934181205</v>
       </c>
       <c r="E6" t="n">
-        <v>78.85443205111687</v>
+        <v>78.87453477864528</v>
       </c>
       <c r="F6" t="n">
-        <v>82.97714589095726</v>
+        <v>82.99907613917006</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>79.61</v>
+        <v>79.62</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>81.15000000000001</v>
+        <v>81.17</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>81.67</v>
+        <v>81.69</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.5</v>
+        <v>74.45</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39131.30728097478</v>
+        <v>100249.4059869257</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4639286728662899</v>
+        <v>1.188525942698579</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.94264839440076</v>
+        <v>79.39005754264367</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65.70169919839807</v>
+        <v>83.85972969254109</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>100249.4059869257</v>
+        <v>41889.45190957077</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.188525942698579</v>
+        <v>0.4966283822813122</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>69.95249740798987</v>
+        <v>92.91638664140675</v>
       </c>
       <c r="F11" t="n">
-        <v>55.31291185760276</v>
+        <v>73.47094235174579</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>65.70169919839807</v>
+        <v>83.85972969254109</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.88622064963147</v>
+        <v>68.37892975101269</v>
       </c>
       <c r="C2" t="n">
-        <v>69.01076201015624</v>
+        <v>72.41240303759825</v>
       </c>
       <c r="D2" t="n">
-        <v>73.13530337068104</v>
+        <v>76.44587632418384</v>
       </c>
       <c r="E2" t="n">
-        <v>77.25984473120582</v>
+        <v>80.47934961076942</v>
       </c>
       <c r="F2" t="n">
-        <v>81.3843860917306</v>
+        <v>84.51282289735499</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.28989316149134</v>
+        <v>69.8510203602426</v>
       </c>
       <c r="C3" t="n">
-        <v>69.41443452201611</v>
+        <v>73.88449364682816</v>
       </c>
       <c r="D3" t="n">
-        <v>73.5389758825409</v>
+        <v>77.91796693341375</v>
       </c>
       <c r="E3" t="n">
-        <v>77.66351724306568</v>
+        <v>81.95144021999933</v>
       </c>
       <c r="F3" t="n">
-        <v>81.78805860359047</v>
+        <v>85.98491350658492</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.6935656733512</v>
+        <v>71.32311096947252</v>
       </c>
       <c r="C4" t="n">
-        <v>69.81810703387598</v>
+        <v>75.35658425605808</v>
       </c>
       <c r="D4" t="n">
-        <v>73.94264839440076</v>
+        <v>79.39005754264367</v>
       </c>
       <c r="E4" t="n">
-        <v>78.06718975492555</v>
+        <v>83.42353082922925</v>
       </c>
       <c r="F4" t="n">
-        <v>82.19173111545034</v>
+        <v>87.45700411581483</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.09723818521107</v>
+        <v>72.79520157870243</v>
       </c>
       <c r="C5" t="n">
-        <v>70.22177954573584</v>
+        <v>76.82867486528799</v>
       </c>
       <c r="D5" t="n">
-        <v>74.34632090626063</v>
+        <v>80.86214815187358</v>
       </c>
       <c r="E5" t="n">
-        <v>78.47086226678542</v>
+        <v>84.89562143845916</v>
       </c>
       <c r="F5" t="n">
-        <v>82.59540362731019</v>
+        <v>88.92909472504475</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.50091069707094</v>
+        <v>74.26729218793236</v>
       </c>
       <c r="C6" t="n">
-        <v>70.62545205759571</v>
+        <v>78.30076547451792</v>
       </c>
       <c r="D6" t="n">
-        <v>74.7499934181205</v>
+        <v>82.33423876110351</v>
       </c>
       <c r="E6" t="n">
-        <v>78.87453477864528</v>
+        <v>86.36771204768908</v>
       </c>
       <c r="F6" t="n">
-        <v>82.99907613917006</v>
+        <v>90.40118533427466</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>79.62</v>
+        <v>80.06</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>81.17</v>
+        <v>80.23999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>81.69</v>
+        <v>80.3</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.39005754264367</v>
+        <v>79.42079644093332</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77.47448376411621</v>
+        <v>77.50967569324308</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.85972969254109</v>
+        <v>83.88007818554388</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.149430670548544</v>
+        <v>1.901906549624759</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41889.45190957077</v>
+        <v>41651.9657631433</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4966283822813122</v>
+        <v>0.4934962145230661</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73.25882950156915</v>
+        <v>74.47801369698664</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>2684.015014147347</v>
+        <v>2685.234198342765</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.47448376411621</v>
+        <v>77.50967569324308</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78.82437016971797</v>
+        <v>78.86141430564098</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.349886405601751</v>
+        <v>-1.351738612397895</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>92.91638664140675</v>
+        <v>92.94212073958076</v>
       </c>
       <c r="F11" t="n">
-        <v>73.47094235174579</v>
+        <v>73.49129084474858</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>83.85972969254109</v>
+        <v>83.88007818554388</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.37892975101269</v>
+        <v>68.40352086964441</v>
       </c>
       <c r="C2" t="n">
-        <v>72.41240303759825</v>
+        <v>72.44006804605895</v>
       </c>
       <c r="D2" t="n">
-        <v>76.44587632418384</v>
+        <v>76.47661522247348</v>
       </c>
       <c r="E2" t="n">
-        <v>80.47934961076942</v>
+        <v>80.51316239888803</v>
       </c>
       <c r="F2" t="n">
-        <v>84.51282289735499</v>
+        <v>84.54970957530259</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.8510203602426</v>
+        <v>69.87561147887432</v>
       </c>
       <c r="C3" t="n">
-        <v>73.88449364682816</v>
+        <v>73.91215865528886</v>
       </c>
       <c r="D3" t="n">
-        <v>77.91796693341375</v>
+        <v>77.94870583170339</v>
       </c>
       <c r="E3" t="n">
-        <v>81.95144021999933</v>
+        <v>81.98525300811795</v>
       </c>
       <c r="F3" t="n">
-        <v>85.98491350658492</v>
+        <v>86.02180018453249</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.32311096947252</v>
+        <v>71.34770208810424</v>
       </c>
       <c r="C4" t="n">
-        <v>75.35658425605808</v>
+        <v>75.38424926451879</v>
       </c>
       <c r="D4" t="n">
-        <v>79.39005754264367</v>
+        <v>79.42079644093332</v>
       </c>
       <c r="E4" t="n">
-        <v>83.42353082922925</v>
+        <v>83.45734361734786</v>
       </c>
       <c r="F4" t="n">
-        <v>87.45700411581483</v>
+        <v>87.49389079376242</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.79520157870243</v>
+        <v>72.81979269733415</v>
       </c>
       <c r="C5" t="n">
-        <v>76.82867486528799</v>
+        <v>76.85633987374869</v>
       </c>
       <c r="D5" t="n">
-        <v>80.86214815187358</v>
+        <v>80.89288705016324</v>
       </c>
       <c r="E5" t="n">
-        <v>84.89562143845916</v>
+        <v>84.92943422657778</v>
       </c>
       <c r="F5" t="n">
-        <v>88.92909472504475</v>
+        <v>88.96598140299233</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74.26729218793236</v>
+        <v>74.29188330656407</v>
       </c>
       <c r="C6" t="n">
-        <v>78.30076547451792</v>
+        <v>78.32843048297862</v>
       </c>
       <c r="D6" t="n">
-        <v>82.33423876110351</v>
+        <v>82.36497765939315</v>
       </c>
       <c r="E6" t="n">
-        <v>86.36771204768908</v>
+        <v>86.40152483580769</v>
       </c>
       <c r="F6" t="n">
-        <v>90.40118533427466</v>
+        <v>90.43807201222225</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>80.06</v>
+        <v>80.09</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>80.23999999999999</v>
+        <v>80.27</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>80.3</v>
+        <v>80.33</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.45</v>
+        <v>67.98999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41651.9657631433</v>
+        <v>1.664531887438219e-24</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4934962145230661</v>
+        <v>1.97215226305253e-29</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67.98999999999999</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.98999999999999</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.664531887438219e-24</v>
+        <v>10261.24711969346</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>0.1215761733467892</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.8</v>
+        <v>64.33</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10261.24711969346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1215761733467892</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -1284,7 +1284,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64.33</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67.59999999999999</v>
+        <v>69.27</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.27</v>
+        <v>72.45</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>24451.57198591053</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.2897044111388051</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.45</v>
+        <v>70.72</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24451.57198591053</v>
+        <v>9573.231368604116</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2897044111388051</v>
+        <v>0.1134245012114183</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.72</v>
+        <v>72.27</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9573.231368604116</v>
+        <v>22903.53654595955</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1134245012114183</v>
+        <v>0.2713631488342212</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.27</v>
+        <v>70.06999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22903.53654595955</v>
+        <v>3983.97526701872</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2713631488342212</v>
+        <v>0.04720249517651789</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.42079644093332</v>
+        <v>79.61084415916976</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77.50967569324308</v>
+        <v>77.72897076212392</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.88007818554388</v>
+        <v>84.00188208561003</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.901906549624759</v>
+        <v>1.902503567955629</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3983.97526701872</v>
+        <v>2343.421744894764</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04720249517651789</v>
+        <v>0.02779808994074086</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>721.7479997247373</v>
+        <v>731.7008399645036</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.47801369698664</v>
+        <v>72.1224006836284</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>2685.234198342765</v>
+        <v>2692.831425569173</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.50967569324308</v>
+        <v>77.72897076212392</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78.86141430564098</v>
+        <v>79.08410963475143</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.351738612397895</v>
+        <v>-1.355138872627506</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>92.94212073958076</v>
+        <v>93.09616229547635</v>
       </c>
       <c r="F11" t="n">
-        <v>73.49129084474858</v>
+        <v>73.61309474481473</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>83.88007818554388</v>
+        <v>84.00188208561003</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.40352086964441</v>
+        <v>68.55555904423355</v>
       </c>
       <c r="C2" t="n">
-        <v>72.44006804605895</v>
+        <v>72.61111099247174</v>
       </c>
       <c r="D2" t="n">
-        <v>76.47661522247348</v>
+        <v>76.66666294070993</v>
       </c>
       <c r="E2" t="n">
-        <v>80.51316239888803</v>
+        <v>80.72221488894812</v>
       </c>
       <c r="F2" t="n">
-        <v>84.54970957530259</v>
+        <v>84.77776683718629</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.87561147887432</v>
+        <v>70.02764965346347</v>
       </c>
       <c r="C3" t="n">
-        <v>73.91215865528886</v>
+        <v>74.08320160170166</v>
       </c>
       <c r="D3" t="n">
-        <v>77.94870583170339</v>
+        <v>78.13875354993984</v>
       </c>
       <c r="E3" t="n">
-        <v>81.98525300811795</v>
+        <v>82.19430549817803</v>
       </c>
       <c r="F3" t="n">
-        <v>86.02180018453249</v>
+        <v>86.2498574464162</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.34770208810424</v>
+        <v>71.49974026269338</v>
       </c>
       <c r="C4" t="n">
-        <v>75.38424926451879</v>
+        <v>75.55529221093157</v>
       </c>
       <c r="D4" t="n">
-        <v>79.42079644093332</v>
+        <v>79.61084415916976</v>
       </c>
       <c r="E4" t="n">
-        <v>83.45734361734786</v>
+        <v>83.66639610740795</v>
       </c>
       <c r="F4" t="n">
-        <v>87.49389079376242</v>
+        <v>87.72194805564612</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.81979269733415</v>
+        <v>72.9718308719233</v>
       </c>
       <c r="C5" t="n">
-        <v>76.85633987374869</v>
+        <v>77.02738282016149</v>
       </c>
       <c r="D5" t="n">
-        <v>80.89288705016324</v>
+        <v>81.08293476839967</v>
       </c>
       <c r="E5" t="n">
-        <v>84.92943422657778</v>
+        <v>85.13848671663786</v>
       </c>
       <c r="F5" t="n">
-        <v>88.96598140299233</v>
+        <v>89.19403866487605</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74.29188330656407</v>
+        <v>74.44392148115321</v>
       </c>
       <c r="C6" t="n">
-        <v>78.32843048297862</v>
+        <v>78.4994734293914</v>
       </c>
       <c r="D6" t="n">
-        <v>82.36497765939315</v>
+        <v>82.55502537762959</v>
       </c>
       <c r="E6" t="n">
-        <v>86.40152483580769</v>
+        <v>86.61057732586778</v>
       </c>
       <c r="F6" t="n">
-        <v>90.43807201222225</v>
+        <v>90.66612927410596</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>80.09</v>
+        <v>80.28</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>80.27</v>
+        <v>80.45999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>80.33</v>
+        <v>80.52</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2343.421744894764</v>
+        <v>2343.421744894763</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2343.421744894763</v>
+        <v>2343.421744894764</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.06999999999999</v>
+        <v>71.91</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2343.421744894764</v>
+        <v>18151.43130181984</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02779808994074086</v>
+        <v>0.2153155406108199</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.91</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18151.43130181984</v>
+        <v>51652.35822791902</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2153155406108199</v>
+        <v>0.6127095572101291</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.81</v>
+        <v>79.955</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51652.35822791902</v>
+        <v>87257.83056347823</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6127095572101291</v>
+        <v>1.03506806972401</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.61084415916976</v>
+        <v>83.25263579655061</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77.72897076212392</v>
+        <v>81.47795041474325</v>
       </c>
     </row>
     <row r="8">
@@ -512,27 +512,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84.00188208561003</v>
+        <v>87.39356835410116</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>12M TC cycle input Aframax ($/day)</t>
+          <t>12M TC cycle input Suezmax ($/day)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56250</v>
+        <v>61250</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12M FFA strip Aframax ($/day)</t>
+          <t>12M FFA strip Suezmax ($/day)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77250</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.902503567955629</v>
+        <v>1.905816800374504</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87257.83056347823</v>
+        <v>54687.50808311134</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.03506806972401</v>
+        <v>0.6715083471709065</v>
       </c>
     </row>
   </sheetData>
@@ -608,11 +608,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>731.7008399645036</v>
+        <v>934.8801494892942</v>
       </c>
     </row>
     <row r="3">
@@ -644,43 +644,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>795.5721849210412</v>
+        <v>794.3943948101116</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fleet value — VLCC</t>
+          <t>+ Cash &amp; equivalents</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.1224006836284</v>
+        <v>996.151</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Cash &amp; equivalents</t>
+          <t>+ Working capital (net)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>996.151</v>
+        <v>97.285</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>+ Working capital (net)</t>
+          <t>- Total debt</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>97.285</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>- Total debt</t>
+          <t>- Lease liabilities</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -690,7 +690,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>- Lease liabilities</t>
+          <t>- Newbuild commitments</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -700,70 +700,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>- Newbuild commitments</t>
+          <t>+ Newbuild advances</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>+ Newbuild advances</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
+      <c r="A10">
         <f> NAV total</f>
         <v/>
       </c>
+      <c r="B10" t="n">
+        <v>2822.710544299406</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Diluted shares</t>
+        </is>
+      </c>
       <c r="B11" t="n">
-        <v>2692.831425569173</v>
+        <v>34643858</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Diluted shares</t>
+          <t>NAV / share</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34643858</v>
+        <v>81.47795041474325</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NAV / share</t>
+          <t>NAV / share (ex yard discount)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.72897076212392</v>
+        <v>82.6967152655358</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NAV / share (ex yard discount)</t>
+          <t>Yard-discount impact / share</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>79.08410963475143</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Yard-discount impact / share</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-1.355138872627506</v>
+        <v>-1.218764850792553</v>
       </c>
     </row>
   </sheetData>
@@ -796,7 +786,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FFA spot Aframax ($/day)</t>
+          <t>FFA spot Suezmax ($/day)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -827,19 +817,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75000</v>
+        <v>81500</v>
       </c>
       <c r="C2" t="n">
-        <v>68400</v>
+        <v>76517.33</v>
       </c>
       <c r="D2" t="n">
-        <v>5.085959812667226</v>
+        <v>5.143274789801485</v>
       </c>
       <c r="E2" t="n">
-        <v>1.521489953166806</v>
+        <v>1.535818697450371</v>
       </c>
       <c r="F2" t="n">
-        <v>1.482307630488001</v>
+        <v>1.496267372346717</v>
       </c>
     </row>
     <row r="3">
@@ -849,19 +839,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88000</v>
+        <v>99000</v>
       </c>
       <c r="C3" t="n">
-        <v>78540</v>
+        <v>90342.33</v>
       </c>
       <c r="D3" t="n">
-        <v>6.123030388243712</v>
+        <v>6.188776424247049</v>
       </c>
       <c r="E3" t="n">
-        <v>1.780757597060928</v>
+        <v>1.797194106061762</v>
       </c>
       <c r="F3" t="n">
-        <v>1.690220311747387</v>
+        <v>1.705821155687786</v>
       </c>
     </row>
     <row r="4">
@@ -871,19 +861,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82000</v>
+        <v>92000</v>
       </c>
       <c r="C4" t="n">
-        <v>73860</v>
+        <v>84812.33</v>
       </c>
       <c r="D4" t="n">
-        <v>5.67087395946202</v>
+        <v>5.740495765811144</v>
       </c>
       <c r="E4" t="n">
-        <v>1.667718489865505</v>
+        <v>1.685123941452786</v>
       </c>
       <c r="F4" t="n">
-        <v>1.54216381843744</v>
+        <v>1.55825889554103</v>
       </c>
     </row>
     <row r="5">
@@ -893,19 +883,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64000</v>
+        <v>67500</v>
       </c>
       <c r="C5" t="n">
-        <v>59820</v>
+        <v>65457.33</v>
       </c>
       <c r="D5" t="n">
-        <v>4.24718270822349</v>
+        <v>4.284313478751775</v>
       </c>
       <c r="E5" t="n">
-        <v>1.311795677055873</v>
+        <v>1.321078369687944</v>
       </c>
       <c r="F5" t="n">
-        <v>1.181797907257543</v>
+        <v>1.190160693412562</v>
       </c>
     </row>
     <row r="6">
@@ -915,19 +905,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59000</v>
+        <v>60000</v>
       </c>
       <c r="C6" t="n">
-        <v>55920</v>
+        <v>59532.33</v>
       </c>
       <c r="D6" t="n">
-        <v>3.831544089647868</v>
+        <v>3.857727067316305</v>
       </c>
       <c r="E6" t="n">
-        <v>1.207886022411967</v>
+        <v>1.214431766829076</v>
       </c>
       <c r="F6" t="n">
-        <v>1.060161996779837</v>
+        <v>1.06590719901158</v>
       </c>
     </row>
     <row r="7">
@@ -937,19 +927,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70000</v>
+        <v>78000</v>
       </c>
       <c r="C7" t="n">
-        <v>64500</v>
+        <v>73752.33</v>
       </c>
       <c r="D7" t="n">
-        <v>4.781661505843259</v>
+        <v>4.843934448939333</v>
       </c>
       <c r="E7" t="n">
-        <v>1.445415376460815</v>
+        <v>1.460983612234833</v>
       </c>
       <c r="F7" t="n">
-        <v>1.235970776352604</v>
+        <v>1.249283132627081</v>
       </c>
     </row>
     <row r="8">
@@ -959,19 +949,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74000</v>
+        <v>81500</v>
       </c>
       <c r="C8" t="n">
-        <v>67620</v>
+        <v>76517.33</v>
       </c>
       <c r="D8" t="n">
-        <v>5.050624867436819</v>
+        <v>5.105674783979385</v>
       </c>
       <c r="E8" t="n">
-        <v>1.512656216859205</v>
+        <v>1.526418695994846</v>
       </c>
       <c r="F8" t="n">
-        <v>1.26015806643379</v>
+        <v>1.271623261832197</v>
       </c>
     </row>
     <row r="9">
@@ -981,19 +971,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56000</v>
+        <v>56500</v>
       </c>
       <c r="C9" t="n">
-        <v>53580</v>
+        <v>56767.33</v>
       </c>
       <c r="D9" t="n">
-        <v>3.613016077229332</v>
+        <v>3.633586738098352</v>
       </c>
       <c r="E9" t="n">
-        <v>1.153254019307333</v>
+        <v>1.158396684524588</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9360068332987037</v>
+        <v>0.9401807357556916</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +993,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10.3887873407953</v>
+        <v>10.47750244621465</v>
       </c>
     </row>
     <row r="11">
@@ -1013,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>93.09616229547635</v>
+        <v>97.27332589008626</v>
       </c>
       <c r="F11" t="n">
-        <v>73.61309474481473</v>
+        <v>76.91606590788652</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>84.00188208561003</v>
+        <v>87.39356835410116</v>
       </c>
     </row>
     <row r="13">
@@ -1036,7 +1026,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77250</v>
+        <v>85000</v>
       </c>
     </row>
   </sheetData>
@@ -1100,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.55555904423355</v>
+        <v>71.42089598685779</v>
       </c>
       <c r="C2" t="n">
-        <v>72.61111099247174</v>
+        <v>75.83095785907227</v>
       </c>
       <c r="D2" t="n">
-        <v>76.66666294070993</v>
+        <v>80.24101973128673</v>
       </c>
       <c r="E2" t="n">
-        <v>80.72221488894812</v>
+        <v>84.6510816035012</v>
       </c>
       <c r="F2" t="n">
-        <v>84.77776683718629</v>
+        <v>89.06114347571564</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70.02764965346347</v>
+        <v>72.92670401948973</v>
       </c>
       <c r="C3" t="n">
-        <v>74.08320160170166</v>
+        <v>77.3367658917042</v>
       </c>
       <c r="D3" t="n">
-        <v>78.13875354993984</v>
+        <v>81.74682776391867</v>
       </c>
       <c r="E3" t="n">
-        <v>82.19430549817803</v>
+        <v>86.15688963613314</v>
       </c>
       <c r="F3" t="n">
-        <v>86.2498574464162</v>
+        <v>90.56695150834759</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.49974026269338</v>
+        <v>74.43251205212168</v>
       </c>
       <c r="C4" t="n">
-        <v>75.55529221093157</v>
+        <v>78.84257392433616</v>
       </c>
       <c r="D4" t="n">
-        <v>79.61084415916976</v>
+        <v>83.25263579655061</v>
       </c>
       <c r="E4" t="n">
-        <v>83.66639610740795</v>
+        <v>87.66269766876509</v>
       </c>
       <c r="F4" t="n">
-        <v>87.72194805564612</v>
+        <v>92.07275954097953</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.9718308719233</v>
+        <v>75.93832008475363</v>
       </c>
       <c r="C5" t="n">
-        <v>77.02738282016149</v>
+        <v>80.34838195696811</v>
       </c>
       <c r="D5" t="n">
-        <v>81.08293476839967</v>
+        <v>84.75844382918257</v>
       </c>
       <c r="E5" t="n">
-        <v>85.13848671663786</v>
+        <v>89.16850570139702</v>
       </c>
       <c r="F5" t="n">
-        <v>89.19403866487605</v>
+        <v>93.57856757361148</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74.44392148115321</v>
+        <v>77.44412811738557</v>
       </c>
       <c r="C6" t="n">
-        <v>78.4994734293914</v>
+        <v>81.85418998960006</v>
       </c>
       <c r="D6" t="n">
-        <v>82.55502537762959</v>
+        <v>86.26425186181451</v>
       </c>
       <c r="E6" t="n">
-        <v>86.61057732586778</v>
+        <v>90.67431373402897</v>
       </c>
       <c r="F6" t="n">
-        <v>90.66612927410596</v>
+        <v>95.08437560624343</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>80.28</v>
+        <v>83.93000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>80.45999999999999</v>
+        <v>84.11</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>80.52</v>
+        <v>84.18000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1284,13 +1274,6 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
           <t>Aframax FFA forward curve is CONSTRUCTED (no market anchor) — built from the 12M TC + spot, not a Baltic / $MT / Worldscale series. Treat its dividend-strip contribution as indicative.</t>
         </is>
       </c>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>83.25263579655061</v>
+        <v>79.61084415916976</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>81.47795041474325</v>
+        <v>77.72897076212392</v>
       </c>
     </row>
     <row r="8">
@@ -512,27 +512,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87.39356835410116</v>
+        <v>84.00188208561003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>12M TC cycle input Suezmax ($/day)</t>
+          <t>12M TC cycle input Aframax ($/day)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61250</v>
+        <v>56250</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12M FFA strip Suezmax ($/day)</t>
+          <t>12M FFA strip Aframax ($/day)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85000</v>
+        <v>77250</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.905816800374504</v>
+        <v>1.902503567955629</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54687.50808311134</v>
+        <v>87257.83056347823</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6715083471709065</v>
+        <v>1.03506806972401</v>
       </c>
     </row>
   </sheetData>
@@ -608,11 +608,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>934.8801494892942</v>
+        <v>731.7008399645036</v>
       </c>
     </row>
     <row r="3">
@@ -644,43 +644,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>794.3943948101116</v>
+        <v>795.5721849210412</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>+ Cash &amp; equivalents</t>
+          <t>Fleet value — VLCC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>996.151</v>
+        <v>72.1224006836284</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Working capital (net)</t>
+          <t>+ Cash &amp; equivalents</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97.285</v>
+        <v>996.151</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>- Total debt</t>
+          <t>+ Working capital (net)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0</v>
+        <v>97.285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>- Lease liabilities</t>
+          <t>- Total debt</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -690,7 +690,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>- Newbuild commitments</t>
+          <t>- Lease liabilities</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -700,60 +700,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>- Newbuild commitments</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>+ Newbuild advances</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10">
+    <row r="11">
+      <c r="A11">
         <f> NAV total</f>
         <v/>
       </c>
-      <c r="B10" t="n">
-        <v>2822.710544299406</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Diluted shares</t>
-        </is>
-      </c>
       <c r="B11" t="n">
-        <v>34643858</v>
+        <v>2692.831425569173</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAV / share</t>
+          <t>Diluted shares</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81.47795041474325</v>
+        <v>34643858</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NAV / share (ex yard discount)</t>
+          <t>NAV / share</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>82.6967152655358</v>
+        <v>77.72897076212392</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>NAV / share (ex yard discount)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>79.08410963475143</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Yard-discount impact / share</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>-1.218764850792553</v>
+      <c r="B15" t="n">
+        <v>-1.355138872627506</v>
       </c>
     </row>
   </sheetData>
@@ -786,7 +796,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FFA spot Suezmax ($/day)</t>
+          <t>FFA spot Aframax ($/day)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -817,19 +827,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81500</v>
+        <v>75000</v>
       </c>
       <c r="C2" t="n">
-        <v>76517.33</v>
+        <v>68400</v>
       </c>
       <c r="D2" t="n">
-        <v>5.143274789801485</v>
+        <v>5.085959812667226</v>
       </c>
       <c r="E2" t="n">
-        <v>1.535818697450371</v>
+        <v>1.521489953166806</v>
       </c>
       <c r="F2" t="n">
-        <v>1.496267372346717</v>
+        <v>1.482307630488001</v>
       </c>
     </row>
     <row r="3">
@@ -839,19 +849,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99000</v>
+        <v>88000</v>
       </c>
       <c r="C3" t="n">
-        <v>90342.33</v>
+        <v>78540</v>
       </c>
       <c r="D3" t="n">
-        <v>6.188776424247049</v>
+        <v>6.123030388243712</v>
       </c>
       <c r="E3" t="n">
-        <v>1.797194106061762</v>
+        <v>1.780757597060928</v>
       </c>
       <c r="F3" t="n">
-        <v>1.705821155687786</v>
+        <v>1.690220311747387</v>
       </c>
     </row>
     <row r="4">
@@ -861,19 +871,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92000</v>
+        <v>82000</v>
       </c>
       <c r="C4" t="n">
-        <v>84812.33</v>
+        <v>73860</v>
       </c>
       <c r="D4" t="n">
-        <v>5.740495765811144</v>
+        <v>5.67087395946202</v>
       </c>
       <c r="E4" t="n">
-        <v>1.685123941452786</v>
+        <v>1.667718489865505</v>
       </c>
       <c r="F4" t="n">
-        <v>1.55825889554103</v>
+        <v>1.54216381843744</v>
       </c>
     </row>
     <row r="5">
@@ -883,19 +893,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67500</v>
+        <v>64000</v>
       </c>
       <c r="C5" t="n">
-        <v>65457.33</v>
+        <v>59820</v>
       </c>
       <c r="D5" t="n">
-        <v>4.284313478751775</v>
+        <v>4.24718270822349</v>
       </c>
       <c r="E5" t="n">
-        <v>1.321078369687944</v>
+        <v>1.311795677055873</v>
       </c>
       <c r="F5" t="n">
-        <v>1.190160693412562</v>
+        <v>1.181797907257543</v>
       </c>
     </row>
     <row r="6">
@@ -905,19 +915,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60000</v>
+        <v>59000</v>
       </c>
       <c r="C6" t="n">
-        <v>59532.33</v>
+        <v>55920</v>
       </c>
       <c r="D6" t="n">
-        <v>3.857727067316305</v>
+        <v>3.831544089647868</v>
       </c>
       <c r="E6" t="n">
-        <v>1.214431766829076</v>
+        <v>1.207886022411967</v>
       </c>
       <c r="F6" t="n">
-        <v>1.06590719901158</v>
+        <v>1.060161996779837</v>
       </c>
     </row>
     <row r="7">
@@ -927,19 +937,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78000</v>
+        <v>70000</v>
       </c>
       <c r="C7" t="n">
-        <v>73752.33</v>
+        <v>64500</v>
       </c>
       <c r="D7" t="n">
-        <v>4.843934448939333</v>
+        <v>4.781661505843259</v>
       </c>
       <c r="E7" t="n">
-        <v>1.460983612234833</v>
+        <v>1.445415376460815</v>
       </c>
       <c r="F7" t="n">
-        <v>1.249283132627081</v>
+        <v>1.235970776352604</v>
       </c>
     </row>
     <row r="8">
@@ -949,19 +959,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81500</v>
+        <v>74000</v>
       </c>
       <c r="C8" t="n">
-        <v>76517.33</v>
+        <v>67620</v>
       </c>
       <c r="D8" t="n">
-        <v>5.105674783979385</v>
+        <v>5.050624867436819</v>
       </c>
       <c r="E8" t="n">
-        <v>1.526418695994846</v>
+        <v>1.512656216859205</v>
       </c>
       <c r="F8" t="n">
-        <v>1.271623261832197</v>
+        <v>1.26015806643379</v>
       </c>
     </row>
     <row r="9">
@@ -971,19 +981,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56500</v>
+        <v>56000</v>
       </c>
       <c r="C9" t="n">
-        <v>56767.33</v>
+        <v>53580</v>
       </c>
       <c r="D9" t="n">
-        <v>3.633586738098352</v>
+        <v>3.613016077229332</v>
       </c>
       <c r="E9" t="n">
-        <v>1.158396684524588</v>
+        <v>1.153254019307333</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9401807357556916</v>
+        <v>0.9360068332987037</v>
       </c>
     </row>
     <row r="10">
@@ -993,7 +1003,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10.47750244621465</v>
+        <v>10.3887873407953</v>
       </c>
     </row>
     <row r="11">
@@ -1003,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>97.27332589008626</v>
+        <v>93.09616229547635</v>
       </c>
       <c r="F11" t="n">
-        <v>76.91606590788652</v>
+        <v>73.61309474481473</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>87.39356835410116</v>
+        <v>84.00188208561003</v>
       </c>
     </row>
     <row r="13">
@@ -1026,7 +1036,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85000</v>
+        <v>77250</v>
       </c>
     </row>
   </sheetData>
@@ -1090,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71.42089598685779</v>
+        <v>68.55555904423355</v>
       </c>
       <c r="C2" t="n">
-        <v>75.83095785907227</v>
+        <v>72.61111099247174</v>
       </c>
       <c r="D2" t="n">
-        <v>80.24101973128673</v>
+        <v>76.66666294070993</v>
       </c>
       <c r="E2" t="n">
-        <v>84.6510816035012</v>
+        <v>80.72221488894812</v>
       </c>
       <c r="F2" t="n">
-        <v>89.06114347571564</v>
+        <v>84.77776683718629</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.92670401948973</v>
+        <v>70.02764965346347</v>
       </c>
       <c r="C3" t="n">
-        <v>77.3367658917042</v>
+        <v>74.08320160170166</v>
       </c>
       <c r="D3" t="n">
-        <v>81.74682776391867</v>
+        <v>78.13875354993984</v>
       </c>
       <c r="E3" t="n">
-        <v>86.15688963613314</v>
+        <v>82.19430549817803</v>
       </c>
       <c r="F3" t="n">
-        <v>90.56695150834759</v>
+        <v>86.2498574464162</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.43251205212168</v>
+        <v>71.49974026269338</v>
       </c>
       <c r="C4" t="n">
-        <v>78.84257392433616</v>
+        <v>75.55529221093157</v>
       </c>
       <c r="D4" t="n">
-        <v>83.25263579655061</v>
+        <v>79.61084415916976</v>
       </c>
       <c r="E4" t="n">
-        <v>87.66269766876509</v>
+        <v>83.66639610740795</v>
       </c>
       <c r="F4" t="n">
-        <v>92.07275954097953</v>
+        <v>87.72194805564612</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.93832008475363</v>
+        <v>72.9718308719233</v>
       </c>
       <c r="C5" t="n">
-        <v>80.34838195696811</v>
+        <v>77.02738282016149</v>
       </c>
       <c r="D5" t="n">
-        <v>84.75844382918257</v>
+        <v>81.08293476839967</v>
       </c>
       <c r="E5" t="n">
-        <v>89.16850570139702</v>
+        <v>85.13848671663786</v>
       </c>
       <c r="F5" t="n">
-        <v>93.57856757361148</v>
+        <v>89.19403866487605</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77.44412811738557</v>
+        <v>74.44392148115321</v>
       </c>
       <c r="C6" t="n">
-        <v>81.85418998960006</v>
+        <v>78.4994734293914</v>
       </c>
       <c r="D6" t="n">
-        <v>86.26425186181451</v>
+        <v>82.55502537762959</v>
       </c>
       <c r="E6" t="n">
-        <v>90.67431373402897</v>
+        <v>86.61057732586778</v>
       </c>
       <c r="F6" t="n">
-        <v>95.08437560624343</v>
+        <v>90.66612927410596</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>83.93000000000001</v>
+        <v>80.28</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>84.11</v>
+        <v>80.45999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>84.18000000000001</v>
+        <v>80.52</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1274,6 +1284,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Aframax FFA forward curve is CONSTRUCTED (no market anchor) — built from the 12M TC + spot, not a Baltic / $MT / Worldscale series. Treat its dividend-strip contribution as indicative.</t>
         </is>
       </c>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79.955</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87257.83056347823</v>
+        <v>64021.93124678641</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.03506806972401</v>
+        <v>0.7594396556467973</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.61084415916976</v>
+        <v>86.17391154557424</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77.72897076212392</v>
+        <v>84.60253946986694</v>
       </c>
     </row>
     <row r="8">
@@ -512,27 +512,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84.00188208561003</v>
+        <v>89.84044638889131</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>12M TC cycle input Aframax ($/day)</t>
+          <t>12M TC cycle input Suezmax ($/day)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56250</v>
+        <v>61250</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12M FFA strip Aframax ($/day)</t>
+          <t>12M FFA strip Suezmax ($/day)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77250</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.902503567955629</v>
+        <v>1.905816800374504</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>64021.93124678641</v>
+        <v>8968.20096005224</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7594396556467973</v>
+        <v>0.1101206109927142</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>731.7008399645036</v>
+        <v>934.8801494892942</v>
       </c>
     </row>
     <row r="3">
@@ -644,43 +644,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>795.5721849210412</v>
+        <v>794.3943948101116</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fleet value — VLCC</t>
+          <t>+ Cash &amp; equivalents</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.1224006836284</v>
+        <v>1211.589</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Cash &amp; equivalents</t>
+          <t>+ Working capital (net)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>996.151</v>
+        <v>149.762</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>+ Working capital (net)</t>
+          <t>- Total debt</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>97.285</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>- Total debt</t>
+          <t>- Lease liabilities</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -690,80 +690,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>- Lease liabilities</t>
+          <t>- Newbuild commitments</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0</v>
+        <v>-156.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>- Newbuild commitments</t>
+          <t>+ Newbuild advances</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>+ Newbuild advances</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
+      <c r="A10">
         <f> NAV total</f>
         <v/>
       </c>
+      <c r="B10" t="n">
+        <v>2934.025544299406</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Diluted shares</t>
+        </is>
+      </c>
       <c r="B11" t="n">
-        <v>2692.831425569173</v>
+        <v>34680112</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Diluted shares</t>
+          <t>NAV / share</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34643858</v>
+        <v>84.60253946986694</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NAV / share</t>
+          <t>NAV / share (ex yard discount)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.72897076212392</v>
+        <v>85.82003024458672</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NAV / share (ex yard discount)</t>
+          <t>Yard-discount impact / share</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>79.08410963475143</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Yard-discount impact / share</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-1.355138872627506</v>
+        <v>-1.217490774719778</v>
       </c>
     </row>
   </sheetData>
@@ -796,7 +786,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FFA spot Aframax ($/day)</t>
+          <t>FFA spot Suezmax ($/day)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -827,19 +817,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75000</v>
+        <v>81500</v>
       </c>
       <c r="C2" t="n">
-        <v>68400</v>
+        <v>76517.33</v>
       </c>
       <c r="D2" t="n">
-        <v>5.085959812667226</v>
+        <v>5.137898097701141</v>
       </c>
       <c r="E2" t="n">
-        <v>1.521489953166806</v>
+        <v>1.534474524425285</v>
       </c>
       <c r="F2" t="n">
-        <v>1.482307630488001</v>
+        <v>1.494957815272328</v>
       </c>
     </row>
     <row r="3">
@@ -849,19 +839,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88000</v>
+        <v>99000</v>
       </c>
       <c r="C3" t="n">
-        <v>78540</v>
+        <v>90342.33</v>
       </c>
       <c r="D3" t="n">
-        <v>6.123030388243712</v>
+        <v>6.182306782497199</v>
       </c>
       <c r="E3" t="n">
-        <v>1.780757597060928</v>
+        <v>1.7955766956243</v>
       </c>
       <c r="F3" t="n">
-        <v>1.690220311747387</v>
+        <v>1.704285977638655</v>
       </c>
     </row>
     <row r="4">
@@ -871,19 +861,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82000</v>
+        <v>92000</v>
       </c>
       <c r="C4" t="n">
-        <v>73860</v>
+        <v>84812.33</v>
       </c>
       <c r="D4" t="n">
-        <v>5.67087395946202</v>
+        <v>5.734494749047019</v>
       </c>
       <c r="E4" t="n">
-        <v>1.667718489865505</v>
+        <v>1.683623687261755</v>
       </c>
       <c r="F4" t="n">
-        <v>1.54216381843744</v>
+        <v>1.556871588422996</v>
       </c>
     </row>
     <row r="5">
@@ -893,19 +883,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64000</v>
+        <v>67500</v>
       </c>
       <c r="C5" t="n">
-        <v>59820</v>
+        <v>65457.33</v>
       </c>
       <c r="D5" t="n">
-        <v>4.24718270822349</v>
+        <v>4.279834730215477</v>
       </c>
       <c r="E5" t="n">
-        <v>1.311795677055873</v>
+        <v>1.319958682553869</v>
       </c>
       <c r="F5" t="n">
-        <v>1.181797907257543</v>
+        <v>1.189151966264747</v>
       </c>
     </row>
     <row r="6">
@@ -915,19 +905,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59000</v>
+        <v>60000</v>
       </c>
       <c r="C6" t="n">
-        <v>55920</v>
+        <v>59532.33</v>
       </c>
       <c r="D6" t="n">
-        <v>3.831544089647868</v>
+        <v>3.85369426496842</v>
       </c>
       <c r="E6" t="n">
-        <v>1.207886022411967</v>
+        <v>1.213423566242105</v>
       </c>
       <c r="F6" t="n">
-        <v>1.060161996779837</v>
+        <v>1.065022300993385</v>
       </c>
     </row>
     <row r="7">
@@ -937,19 +927,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70000</v>
+        <v>78000</v>
       </c>
       <c r="C7" t="n">
-        <v>64500</v>
+        <v>73752.33</v>
       </c>
       <c r="D7" t="n">
-        <v>4.781661505843259</v>
+        <v>4.838870682146657</v>
       </c>
       <c r="E7" t="n">
-        <v>1.445415376460815</v>
+        <v>1.459717670536664</v>
       </c>
       <c r="F7" t="n">
-        <v>1.235970776352604</v>
+        <v>1.248200629307285</v>
       </c>
     </row>
     <row r="8">
@@ -959,19 +949,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74000</v>
+        <v>81500</v>
       </c>
       <c r="C8" t="n">
-        <v>67620</v>
+        <v>76517.33</v>
       </c>
       <c r="D8" t="n">
-        <v>5.050624867436819</v>
+        <v>5.100337398286444</v>
       </c>
       <c r="E8" t="n">
-        <v>1.512656216859205</v>
+        <v>1.525084349571611</v>
       </c>
       <c r="F8" t="n">
-        <v>1.26015806643379</v>
+        <v>1.270511649431497</v>
       </c>
     </row>
     <row r="9">
@@ -981,19 +971,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56000</v>
+        <v>56500</v>
       </c>
       <c r="C9" t="n">
-        <v>53580</v>
+        <v>56767.33</v>
       </c>
       <c r="D9" t="n">
-        <v>3.613016077229332</v>
+        <v>3.62978824824333</v>
       </c>
       <c r="E9" t="n">
-        <v>1.153254019307333</v>
+        <v>1.157447062060833</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9360068332987037</v>
+        <v>0.9394100008609954</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +993,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10.3887873407953</v>
+        <v>10.46841192819189</v>
       </c>
     </row>
     <row r="11">
@@ -1013,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>93.09616229547635</v>
+        <v>100.3793119619646</v>
       </c>
       <c r="F11" t="n">
-        <v>73.61309474481473</v>
+        <v>79.37203446069941</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>84.00188208561003</v>
+        <v>89.84044638889131</v>
       </c>
     </row>
     <row r="13">
@@ -1036,7 +1026,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77250</v>
+        <v>85000</v>
       </c>
     </row>
   </sheetData>
@@ -1100,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.55555904423355</v>
+        <v>74.35454043570167</v>
       </c>
       <c r="C2" t="n">
-        <v>72.61111099247174</v>
+        <v>78.75999210414531</v>
       </c>
       <c r="D2" t="n">
-        <v>76.66666294070993</v>
+        <v>83.16544377258894</v>
       </c>
       <c r="E2" t="n">
-        <v>80.72221488894812</v>
+        <v>87.57089544103256</v>
       </c>
       <c r="F2" t="n">
-        <v>84.77776683718629</v>
+        <v>91.97634710947619</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70.02764965346347</v>
+        <v>75.85877432219431</v>
       </c>
       <c r="C3" t="n">
-        <v>74.08320160170166</v>
+        <v>80.26422599063795</v>
       </c>
       <c r="D3" t="n">
-        <v>78.13875354993984</v>
+        <v>84.66967765908159</v>
       </c>
       <c r="E3" t="n">
-        <v>82.19430549817803</v>
+        <v>89.07512932752522</v>
       </c>
       <c r="F3" t="n">
-        <v>86.2498574464162</v>
+        <v>93.48058099596885</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.49974026269338</v>
+        <v>77.36300820868698</v>
       </c>
       <c r="C4" t="n">
-        <v>75.55529221093157</v>
+        <v>81.76845987713062</v>
       </c>
       <c r="D4" t="n">
-        <v>79.61084415916976</v>
+        <v>86.17391154557424</v>
       </c>
       <c r="E4" t="n">
-        <v>83.66639610740795</v>
+        <v>90.57936321401787</v>
       </c>
       <c r="F4" t="n">
-        <v>87.72194805564612</v>
+        <v>94.98481488246151</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.9718308719233</v>
+        <v>78.86724209517962</v>
       </c>
       <c r="C5" t="n">
-        <v>77.02738282016149</v>
+        <v>83.27269376362327</v>
       </c>
       <c r="D5" t="n">
-        <v>81.08293476839967</v>
+        <v>87.6781454320669</v>
       </c>
       <c r="E5" t="n">
-        <v>85.13848671663786</v>
+        <v>92.08359710051053</v>
       </c>
       <c r="F5" t="n">
-        <v>89.19403866487605</v>
+        <v>96.48904876895415</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74.44392148115321</v>
+        <v>80.37147598167228</v>
       </c>
       <c r="C6" t="n">
-        <v>78.4994734293914</v>
+        <v>84.77692765011592</v>
       </c>
       <c r="D6" t="n">
-        <v>82.55502537762959</v>
+        <v>89.18237931855955</v>
       </c>
       <c r="E6" t="n">
-        <v>86.61057732586778</v>
+        <v>93.58783098700317</v>
       </c>
       <c r="F6" t="n">
-        <v>90.66612927410596</v>
+        <v>97.99328265544682</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>80.28</v>
+        <v>86.84999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>80.45999999999999</v>
+        <v>87.04000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>80.52</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1284,13 +1274,6 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
           <t>Aframax FFA forward curve is CONSTRUCTED (no market anchor) — built from the 12M TC + spot, not a Baltic / $MT / Worldscale series. Treat its dividend-strip contribution as indicative.</t>
         </is>
       </c>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86.17391154557424</v>
+        <v>83.2252509993266</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>89.84044638889131</v>
+        <v>80.01157790139916</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61250</v>
+        <v>58050</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85000</v>
+        <v>88475</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.905816800374504</v>
+        <v>1.783129754520905</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8968.20096005224</v>
+        <v>11450.52924818428</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1101206109927142</v>
+        <v>0.1559861810215845</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +773,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81500</v>
+        <v>118900</v>
       </c>
       <c r="C2" t="n">
-        <v>76517.33</v>
+        <v>106063.33</v>
       </c>
       <c r="D2" t="n">
-        <v>5.137898097701141</v>
+        <v>5.759238551164786</v>
       </c>
       <c r="E2" t="n">
-        <v>1.534474524425285</v>
+        <v>1.689809637791196</v>
       </c>
       <c r="F2" t="n">
-        <v>1.494957815272328</v>
+        <v>1.646292645545614</v>
       </c>
     </row>
     <row r="3">
@@ -839,19 +839,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99000</v>
+        <v>118900</v>
       </c>
       <c r="C3" t="n">
-        <v>90342.33</v>
+        <v>106063.33</v>
       </c>
       <c r="D3" t="n">
-        <v>6.182306782497199</v>
+        <v>5.759238551164786</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7955766956243</v>
+        <v>1.689809637791196</v>
       </c>
       <c r="F3" t="n">
-        <v>1.704285977638655</v>
+        <v>1.603896329009148</v>
       </c>
     </row>
     <row r="4">
@@ -861,19 +861,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92000</v>
+        <v>58050</v>
       </c>
       <c r="C4" t="n">
-        <v>84812.33</v>
+        <v>57991.83</v>
       </c>
       <c r="D4" t="n">
-        <v>5.734494749047019</v>
+        <v>3.508143372662334</v>
       </c>
       <c r="E4" t="n">
-        <v>1.683623687261755</v>
+        <v>1.127035843165583</v>
       </c>
       <c r="F4" t="n">
-        <v>1.556871588422996</v>
+        <v>1.042186622007329</v>
       </c>
     </row>
     <row r="5">
@@ -883,19 +883,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67500</v>
+        <v>58050</v>
       </c>
       <c r="C5" t="n">
-        <v>65457.33</v>
+        <v>57991.83</v>
       </c>
       <c r="D5" t="n">
-        <v>4.279834730215477</v>
+        <v>3.508143372662334</v>
       </c>
       <c r="E5" t="n">
-        <v>1.319958682553869</v>
+        <v>1.127035843165583</v>
       </c>
       <c r="F5" t="n">
-        <v>1.189151966264747</v>
+        <v>1.015347606455481</v>
       </c>
     </row>
     <row r="6">
@@ -905,19 +905,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60000</v>
+        <v>26950</v>
       </c>
       <c r="C6" t="n">
-        <v>59532.33</v>
+        <v>33422.83</v>
       </c>
       <c r="D6" t="n">
-        <v>3.85369426496842</v>
+        <v>2.014648004174915</v>
       </c>
       <c r="E6" t="n">
-        <v>1.213423566242105</v>
+        <v>0.7536620010437287</v>
       </c>
       <c r="F6" t="n">
-        <v>1.065022300993385</v>
+        <v>0.6614894096780063</v>
       </c>
     </row>
     <row r="7">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78000</v>
+        <v>26950</v>
       </c>
       <c r="C7" t="n">
-        <v>73752.33</v>
+        <v>33422.83</v>
       </c>
       <c r="D7" t="n">
-        <v>4.838870682146657</v>
+        <v>2.014648004174915</v>
       </c>
       <c r="E7" t="n">
-        <v>1.459717670536664</v>
+        <v>0.7536620010437287</v>
       </c>
       <c r="F7" t="n">
-        <v>1.248200629307285</v>
+        <v>0.6444543372842191</v>
       </c>
     </row>
     <row r="8">
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81500</v>
+        <v>26950</v>
       </c>
       <c r="C8" t="n">
-        <v>76517.33</v>
+        <v>33422.83</v>
       </c>
       <c r="D8" t="n">
-        <v>5.100337398286444</v>
+        <v>2.014648004174915</v>
       </c>
       <c r="E8" t="n">
-        <v>1.525084349571611</v>
+        <v>0.7536620010437287</v>
       </c>
       <c r="F8" t="n">
-        <v>1.270511649431497</v>
+        <v>0.6278579623014802</v>
       </c>
     </row>
     <row r="9">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56500</v>
+        <v>26950</v>
       </c>
       <c r="C9" t="n">
-        <v>56767.33</v>
+        <v>33422.83</v>
       </c>
       <c r="D9" t="n">
-        <v>3.62978824824333</v>
+        <v>2.014648004174915</v>
       </c>
       <c r="E9" t="n">
-        <v>1.157447062060833</v>
+        <v>0.7536620010437287</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9394100008609954</v>
+        <v>0.6116889871306944</v>
       </c>
     </row>
     <row r="10">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10.46841192819189</v>
+        <v>7.853213899411973</v>
       </c>
     </row>
     <row r="11">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100.3793119619646</v>
+        <v>91.25641014540076</v>
       </c>
       <c r="F11" t="n">
-        <v>79.37203446069941</v>
+        <v>72.1583640019872</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>89.84044638889131</v>
+        <v>80.01157790139916</v>
       </c>
     </row>
     <row r="13">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85000</v>
+        <v>88475</v>
       </c>
     </row>
   </sheetData>
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74.35454043570167</v>
+        <v>72.29047805332831</v>
       </c>
       <c r="C2" t="n">
-        <v>78.75999210414531</v>
+        <v>76.69592972177195</v>
       </c>
       <c r="D2" t="n">
-        <v>83.16544377258894</v>
+        <v>81.10138139021558</v>
       </c>
       <c r="E2" t="n">
-        <v>87.57089544103256</v>
+        <v>85.50683305865921</v>
       </c>
       <c r="F2" t="n">
-        <v>91.97634710947619</v>
+        <v>89.91228472710284</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.85877432219431</v>
+        <v>73.35241285788382</v>
       </c>
       <c r="C3" t="n">
-        <v>80.26422599063795</v>
+        <v>77.75786452632747</v>
       </c>
       <c r="D3" t="n">
-        <v>84.66967765908159</v>
+        <v>82.1633161947711</v>
       </c>
       <c r="E3" t="n">
-        <v>89.07512932752522</v>
+        <v>86.56876786321473</v>
       </c>
       <c r="F3" t="n">
-        <v>93.48058099596885</v>
+        <v>90.97421953165835</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77.36300820868698</v>
+        <v>74.41434766243933</v>
       </c>
       <c r="C4" t="n">
-        <v>81.76845987713062</v>
+        <v>78.81979933088297</v>
       </c>
       <c r="D4" t="n">
-        <v>86.17391154557424</v>
+        <v>83.2252509993266</v>
       </c>
       <c r="E4" t="n">
-        <v>90.57936321401787</v>
+        <v>87.63070266777024</v>
       </c>
       <c r="F4" t="n">
-        <v>94.98481488246151</v>
+        <v>92.03615433621387</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.86724209517962</v>
+        <v>75.47628246699483</v>
       </c>
       <c r="C5" t="n">
-        <v>83.27269376362327</v>
+        <v>79.88173413543848</v>
       </c>
       <c r="D5" t="n">
-        <v>87.6781454320669</v>
+        <v>84.28718580388211</v>
       </c>
       <c r="E5" t="n">
-        <v>92.08359710051053</v>
+        <v>88.69263747232574</v>
       </c>
       <c r="F5" t="n">
-        <v>96.48904876895415</v>
+        <v>93.09808914076937</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80.37147598167228</v>
+        <v>76.53821727155034</v>
       </c>
       <c r="C6" t="n">
-        <v>84.77692765011592</v>
+        <v>80.94366893999398</v>
       </c>
       <c r="D6" t="n">
-        <v>89.18237931855955</v>
+        <v>85.34912060843762</v>
       </c>
       <c r="E6" t="n">
-        <v>93.58783098700317</v>
+        <v>89.75457227688125</v>
       </c>
       <c r="F6" t="n">
-        <v>97.99328265544682</v>
+        <v>94.16002394532488</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>86.84999999999999</v>
+        <v>83.76000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>87.04000000000001</v>
+        <v>83.91</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09999999999999</v>
+        <v>83.95999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77.25</v>
+        <v>80.89</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11450.52924818428</v>
+        <v>49193.33854951311</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1559861810215845</v>
+        <v>0.6701420384788965</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80.89</v>
+        <v>85.13</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49193.33854951311</v>
+        <v>93157.49004336853</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6701420384788965</v>
+        <v>1.269048861451148</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85.13</v>
+        <v>90.03</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93157.49004336853</v>
+        <v>143965.1179490035</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.269048861451148</v>
+        <v>1.961181746489838</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tnk_fv_report.xlsx
+++ b/outputs/tnk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90.03</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>143965.1179490035</v>
+        <v>130174.4760889026</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.961181746489838</v>
+        <v>1.773317106265051</v>
       </c>
     </row>
   </sheetData>
